--- a/docs/Sundial_Customer__c_Field_Design.xlsx
+++ b/docs/Sundial_Customer__c_Field_Design.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2702" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2709" uniqueCount="867">
   <si>
     <t>Sundial Section</t>
   </si>
@@ -526,6 +526,30 @@
     <t>Referral_Email__c</t>
   </si>
   <si>
+    <t>Sales Rep (Required)</t>
+  </si>
+  <si>
+    <t>Sales_Rep__c</t>
+  </si>
+  <si>
+    <t>REFERENCE (User)</t>
+  </si>
+  <si>
+    <t>Sales Rep Sundial User Name Displayed</t>
+  </si>
+  <si>
+    <t>Dealer (based on Sales Rep)</t>
+  </si>
+  <si>
+    <t>Dealer_Display_Name__c</t>
+  </si>
+  <si>
+    <t>Formula (Text)</t>
+  </si>
+  <si>
+    <t>Set automatically from the Sales Rep's dealer.</t>
+  </si>
+  <si>
     <t>Sales Company</t>
   </si>
   <si>
@@ -535,49 +559,37 @@
     <t>Whether Harmon or a dealer originated the sale.</t>
   </si>
   <si>
-    <t>Dealer Name</t>
+    <t>Setter Name</t>
+  </si>
+  <si>
+    <t>Setter_Name__c</t>
+  </si>
+  <si>
+    <t>Text setter name (portal display / non-SF setters).</t>
+  </si>
+  <si>
+    <t>Lead ID</t>
+  </si>
+  <si>
+    <t>Lead_ID__c</t>
+  </si>
+  <si>
+    <t>Assigned Date</t>
+  </si>
+  <si>
+    <t>Assigned_Date__c</t>
+  </si>
+  <si>
+    <t>Date the record was assigned to a rep.</t>
+  </si>
+  <si>
+    <t>Legacy Dealer Name (Do Not Use)</t>
   </si>
   <si>
     <t>Dealer_Name__c</t>
   </si>
   <si>
     <t>Third-party dealer/sales company name.</t>
-  </si>
-  <si>
-    <t>Setter Name</t>
-  </si>
-  <si>
-    <t>Setter_Name__c</t>
-  </si>
-  <si>
-    <t>Text setter name (portal display / non-SF setters).</t>
-  </si>
-  <si>
-    <t>Lead ID</t>
-  </si>
-  <si>
-    <t>Lead_ID__c</t>
-  </si>
-  <si>
-    <t>Harmon Sales Rep</t>
-  </si>
-  <si>
-    <t>Sales_Rep__c</t>
-  </si>
-  <si>
-    <t>REFERENCE (User)</t>
-  </si>
-  <si>
-    <t>Sales Rep Sundial User Name Displayed</t>
-  </si>
-  <si>
-    <t>Assigned Date</t>
-  </si>
-  <si>
-    <t>Assigned_Date__c</t>
-  </si>
-  <si>
-    <t>Date the record was assigned to a rep.</t>
   </si>
   <si>
     <t>Marketing &amp; Outreach</t>
@@ -3001,7 +3013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H339"/>
+  <dimension ref="A1:H340"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.5" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="30.875" style="1" customWidth="1"/>
@@ -4554,10 +4566,10 @@
         <v>171</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>46</v>
+        <v>172</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>28</v>
@@ -4566,7 +4578,7 @@
         <v>14</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -4574,20 +4586,18 @@
         <v>142</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>46</v>
+        <v>176</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>28</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="F61" s="1"/>
       <c r="G61" s="1" t="s">
         <v>146</v>
       </c>
@@ -4600,22 +4610,22 @@
         <v>142</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>146</v>
@@ -4626,25 +4636,25 @@
         <v>142</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -4652,25 +4662,25 @@
         <v>142</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>183</v>
+        <v>17</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>184</v>
+        <v>28</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -4678,16 +4688,16 @@
         <v>142</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>28</v>
@@ -4701,7 +4711,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>189</v>
@@ -4710,7 +4720,7 @@
         <v>190</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>191</v>
@@ -4719,27 +4729,27 @@
         <v>28</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>28</v>
+        <v>195</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>28</v>
@@ -4753,19 +4763,19 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>28</v>
@@ -4779,19 +4789,19 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>28</v>
@@ -4805,71 +4815,71 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>28</v>
+        <v>206</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>207</v>
+        <v>28</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>28</v>
@@ -4883,19 +4893,19 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>28</v>
@@ -4909,19 +4919,19 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>28</v>
+        <v>214</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>28</v>
@@ -4935,19 +4945,19 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>165</v>
+        <v>46</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>215</v>
+        <v>28</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>28</v>
@@ -4961,19 +4971,19 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>107</v>
+        <v>165</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>28</v>
+        <v>219</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>28</v>
@@ -4987,19 +4997,19 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>220</v>
+        <v>28</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>28</v>
@@ -5013,19 +5023,19 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>28</v>
+        <v>224</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>28</v>
@@ -5039,13 +5049,13 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>17</v>
@@ -5065,13 +5075,13 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>17</v>
@@ -5091,13 +5101,13 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>17</v>
@@ -5117,13 +5127,13 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>17</v>
@@ -5143,13 +5153,13 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>17</v>
@@ -5169,16 +5179,16 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>107</v>
+        <v>17</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>28</v>
@@ -5195,13 +5205,13 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>107</v>
@@ -5221,13 +5231,13 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>107</v>
@@ -5247,13 +5257,13 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>107</v>
@@ -5273,13 +5283,13 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>107</v>
@@ -5299,13 +5309,13 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>107</v>
@@ -5325,13 +5335,13 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>107</v>
@@ -5351,13 +5361,13 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>107</v>
@@ -5377,13 +5387,13 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>107</v>
@@ -5403,13 +5413,13 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>107</v>
@@ -5429,13 +5439,13 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>107</v>
@@ -5455,13 +5465,13 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>107</v>
@@ -5481,13 +5491,13 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>107</v>
@@ -5507,16 +5517,16 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>259</v>
+        <v>215</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>28</v>
@@ -5533,19 +5543,19 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>264</v>
+        <v>28</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>28</v>
@@ -5559,19 +5569,19 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>267</v>
+        <v>11</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>28</v>
+        <v>268</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>28</v>
@@ -5585,16 +5595,16 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>46</v>
+        <v>271</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>28</v>
@@ -5611,13 +5621,13 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>46</v>
@@ -5637,13 +5647,13 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>46</v>
@@ -5663,13 +5673,13 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>46</v>
@@ -5689,16 +5699,16 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>28</v>
@@ -5715,16 +5725,16 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>28</v>
@@ -5741,16 +5751,16 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>217</v>
+        <v>283</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>28</v>
@@ -5767,16 +5777,16 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>28</v>
@@ -5793,19 +5803,19 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>283</v>
+        <v>216</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>284</v>
+        <v>46</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>285</v>
+        <v>28</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>28</v>
@@ -5819,7 +5829,7 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>286</v>
@@ -5828,10 +5838,10 @@
         <v>287</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>107</v>
+        <v>288</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>28</v>
+        <v>289</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>28</v>
@@ -5845,16 +5855,16 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>28</v>
@@ -5871,16 +5881,16 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>28</v>
@@ -5897,13 +5907,13 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>46</v>
@@ -5923,13 +5933,13 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>46</v>
@@ -5949,16 +5959,16 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>298</v>
+        <v>46</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>28</v>
@@ -5975,16 +5985,16 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>23</v>
+        <v>302</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>28</v>
@@ -6001,19 +6011,19 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>301</v>
+        <v>263</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>285</v>
+        <v>28</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>28</v>
@@ -6027,19 +6037,19 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>282</v>
+        <v>306</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>284</v>
+        <v>59</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>28</v>
@@ -6053,19 +6063,19 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>46</v>
+        <v>288</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>28</v>
+        <v>308</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>28</v>
@@ -6079,13 +6089,13 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>46</v>
@@ -6105,19 +6115,19 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>183</v>
+        <v>46</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>311</v>
+        <v>28</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>28</v>
@@ -6131,19 +6141,19 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>11</v>
+        <v>172</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>28</v>
+        <v>315</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>28</v>
@@ -6157,16 +6167,16 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>28</v>
@@ -6183,16 +6193,16 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>284</v>
+        <v>107</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>28</v>
@@ -6209,19 +6219,19 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>11</v>
+        <v>288</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>320</v>
+        <v>28</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>28</v>
@@ -6235,19 +6245,19 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>28</v>
+        <v>324</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>28</v>
@@ -6261,19 +6271,19 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>183</v>
+        <v>46</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>325</v>
+        <v>28</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>28</v>
@@ -6287,19 +6297,19 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>11</v>
+        <v>172</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>28</v>
+        <v>329</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>28</v>
@@ -6313,16 +6323,16 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>28</v>
@@ -6339,16 +6349,16 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>28</v>
@@ -6365,13 +6375,13 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>23</v>
@@ -6391,19 +6401,19 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>334</v>
+        <v>305</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>337</v>
+        <v>23</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>338</v>
+        <v>28</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>28</v>
@@ -6417,19 +6427,19 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>262</v>
+        <v>339</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>263</v>
+        <v>340</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>11</v>
+        <v>341</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>264</v>
+        <v>342</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>28</v>
@@ -6443,19 +6453,19 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>339</v>
+        <v>266</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>340</v>
+        <v>267</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>28</v>
+        <v>268</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>28</v>
@@ -6469,16 +6479,16 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>271</v>
+        <v>344</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>28</v>
@@ -6495,16 +6505,16 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>28</v>
@@ -6521,16 +6531,16 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>28</v>
@@ -6547,16 +6557,16 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>345</v>
+        <v>277</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>28</v>
@@ -6573,19 +6583,19 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>298</v>
+        <v>107</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>348</v>
+        <v>28</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>28</v>
@@ -6599,19 +6609,19 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>11</v>
+        <v>302</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>28</v>
+        <v>352</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>28</v>
@@ -6625,16 +6635,16 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>275</v>
+        <v>354</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>28</v>
@@ -6651,19 +6661,19 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>353</v>
+        <v>46</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>354</v>
+        <v>28</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>28</v>
@@ -6677,19 +6687,19 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>356</v>
+        <v>281</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>46</v>
+        <v>357</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>28</v>
+        <v>358</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>28</v>
@@ -6703,19 +6713,19 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>353</v>
+        <v>46</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>359</v>
+        <v>28</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>28</v>
@@ -6729,19 +6739,19 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>46</v>
+        <v>357</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>28</v>
+        <v>363</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>28</v>
@@ -6755,13 +6765,13 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>46</v>
@@ -6781,16 +6791,16 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>28</v>
@@ -6807,16 +6817,16 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>28</v>
@@ -6833,13 +6843,13 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>291</v>
+        <v>371</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>46</v>
@@ -6859,13 +6869,13 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>46</v>
@@ -6885,13 +6895,13 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>371</v>
+        <v>297</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>46</v>
@@ -6911,13 +6921,13 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>46</v>
@@ -6937,13 +6947,13 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>46</v>
@@ -6963,13 +6973,13 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>46</v>
@@ -6989,13 +6999,13 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>46</v>
@@ -7015,16 +7025,16 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>165</v>
+        <v>46</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>28</v>
@@ -7041,16 +7051,16 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>46</v>
+        <v>165</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>28</v>
@@ -7067,13 +7077,13 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>46</v>
@@ -7093,13 +7103,13 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>46</v>
@@ -7119,13 +7129,13 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>116</v>
+        <v>390</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>117</v>
+        <v>391</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>46</v>
@@ -7145,13 +7155,13 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>388</v>
+        <v>116</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>389</v>
+        <v>117</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>46</v>
@@ -7171,16 +7181,16 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>28</v>
@@ -7197,16 +7207,16 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>28</v>
@@ -7223,16 +7233,16 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>28</v>
@@ -7249,16 +7259,16 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>28</v>
@@ -7275,13 +7285,13 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>46</v>
@@ -7301,13 +7311,13 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>46</v>
@@ -7319,24 +7329,24 @@
         <v>28</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>28</v>
@@ -7345,24 +7355,24 @@
         <v>28</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>28</v>
@@ -7379,16 +7389,16 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>28</v>
@@ -7405,13 +7415,13 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>165</v>
@@ -7431,16 +7441,16 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>46</v>
+        <v>165</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>28</v>
@@ -7457,16 +7467,16 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>284</v>
+        <v>46</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>28</v>
@@ -7483,45 +7493,45 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>414</v>
+        <v>338</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>59</v>
+        <v>288</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>417</v>
+        <v>28</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>28</v>
+        <v>421</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>28</v>
@@ -7535,13 +7545,13 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>59</v>
@@ -7561,16 +7571,16 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>28</v>
@@ -7587,16 +7597,16 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>28</v>
@@ -7613,16 +7623,16 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>28</v>
@@ -7639,16 +7649,16 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>28</v>
@@ -7665,19 +7675,19 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>432</v>
+        <v>59</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>433</v>
+        <v>28</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>28</v>
@@ -7691,19 +7701,19 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>368</v>
+        <v>434</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>46</v>
+        <v>436</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>28</v>
+        <v>437</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>28</v>
@@ -7717,13 +7727,13 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D182" s="1" t="s">
         <v>46</v>
@@ -7743,16 +7753,16 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>434</v>
+        <v>373</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>435</v>
+        <v>297</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>165</v>
+        <v>46</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>28</v>
@@ -7769,13 +7779,13 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D184" s="1" t="s">
         <v>165</v>
@@ -7795,19 +7805,19 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>107</v>
+        <v>165</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>440</v>
+        <v>28</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>28</v>
@@ -7821,19 +7831,19 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>107</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>28</v>
+        <v>444</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>28</v>
@@ -7847,16 +7857,16 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>28</v>
@@ -7873,16 +7883,16 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>59</v>
+        <v>165</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>28</v>
@@ -7899,16 +7909,16 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>165</v>
+        <v>59</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>28</v>
@@ -7925,13 +7935,13 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>165</v>
@@ -7951,13 +7961,13 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>165</v>
@@ -7977,16 +7987,16 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>107</v>
+        <v>165</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>28</v>
@@ -8003,16 +8013,16 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>297</v>
+        <v>458</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>298</v>
+        <v>107</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>28</v>
@@ -8029,16 +8039,16 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>457</v>
+        <v>301</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>165</v>
+        <v>302</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>28</v>
@@ -8055,16 +8065,16 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>460</v>
+        <v>165</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>28</v>
@@ -8081,16 +8091,16 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>28</v>
@@ -8107,16 +8117,16 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>165</v>
+        <v>467</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>28</v>
@@ -8125,7 +8135,7 @@
         <v>28</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="H197" s="1" t="s">
         <v>146</v>
@@ -8133,16 +8143,16 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>298</v>
+        <v>165</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>28</v>
@@ -8151,7 +8161,7 @@
         <v>28</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="H198" s="1" t="s">
         <v>146</v>
@@ -8159,16 +8169,16 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>165</v>
+        <v>302</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>28</v>
@@ -8185,16 +8195,16 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>46</v>
+        <v>165</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>28</v>
@@ -8211,16 +8221,16 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>474</v>
+        <v>46</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>28</v>
@@ -8237,16 +8247,16 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>23</v>
+        <v>478</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>28</v>
@@ -8263,16 +8273,16 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>28</v>
@@ -8289,16 +8299,16 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>28</v>
@@ -8315,16 +8325,16 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>28</v>
@@ -8341,19 +8351,19 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>483</v>
+        <v>418</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>486</v>
+        <v>28</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>28</v>
@@ -8367,19 +8377,19 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>28</v>
+        <v>490</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>28</v>
@@ -8393,19 +8403,19 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>491</v>
+        <v>28</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>28</v>
@@ -8419,19 +8429,19 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>28</v>
+        <v>495</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>28</v>
@@ -8445,13 +8455,13 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>11</v>
@@ -8463,21 +8473,21 @@
         <v>28</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>14</v>
+        <v>146</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>11</v>
@@ -8497,19 +8507,19 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>501</v>
+        <v>28</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>28</v>
@@ -8523,16 +8533,16 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="B213" s="1" t="s">
+      <c r="C213" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="C213" s="1" t="s">
+      <c r="D213" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>505</v>
@@ -8549,19 +8559,19 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>28</v>
@@ -8575,19 +8585,19 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>511</v>
+        <v>17</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>28</v>
+        <v>512</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>28</v>
@@ -8601,19 +8611,19 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>17</v>
+        <v>515</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>514</v>
+        <v>28</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>28</v>
@@ -8627,19 +8637,19 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>28</v>
@@ -8653,19 +8663,19 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>28</v>
+        <v>521</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>28</v>
@@ -8679,16 +8689,16 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>284</v>
+        <v>11</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>28</v>
@@ -8705,19 +8715,19 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>6</v>
+        <v>524</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>182</v>
+        <v>525</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>183</v>
+        <v>288</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>522</v>
+        <v>28</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>28</v>
@@ -8731,19 +8741,19 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>523</v>
+        <v>6</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>524</v>
+        <v>171</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>23</v>
+        <v>172</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>28</v>
@@ -8757,7 +8767,7 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>526</v>
+        <v>506</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>527</v>
@@ -8766,7 +8776,7 @@
         <v>528</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>267</v>
+        <v>23</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>529</v>
@@ -8778,24 +8788,24 @@
         <v>14</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>464</v>
+        <v>531</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>465</v>
+        <v>532</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>530</v>
+        <v>271</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>28</v>
@@ -8809,13 +8819,13 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>532</v>
+        <v>468</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>533</v>
+        <v>469</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>534</v>
@@ -8835,7 +8845,7 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>536</v>
@@ -8856,12 +8866,12 @@
         <v>14</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>14</v>
+        <v>146</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>540</v>
@@ -8870,10 +8880,10 @@
         <v>541</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>28</v>
@@ -8887,19 +8897,19 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>28</v>
@@ -8913,19 +8923,19 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>530</v>
+        <v>357</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>28</v>
@@ -8939,19 +8949,19 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>354</v>
+        <v>552</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>28</v>
@@ -8960,24 +8970,24 @@
         <v>14</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>530</v>
+        <v>357</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>553</v>
+        <v>358</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>28</v>
@@ -8986,24 +8996,24 @@
         <v>14</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>14</v>
+        <v>146</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>556</v>
+        <v>534</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>359</v>
+        <v>557</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>28</v>
@@ -9012,24 +9022,24 @@
         <v>14</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>559</v>
+        <v>363</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>28</v>
@@ -9038,24 +9048,24 @@
         <v>14</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>14</v>
+        <v>146</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>534</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>28</v>
@@ -9064,24 +9074,24 @@
         <v>14</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>538</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>28</v>
@@ -9090,24 +9100,24 @@
         <v>14</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>14</v>
+        <v>146</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>28</v>
@@ -9121,19 +9131,19 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>28</v>
@@ -9147,16 +9157,16 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>574</v>
+        <v>534</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>575</v>
@@ -9173,7 +9183,7 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>576</v>
@@ -9199,7 +9209,7 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B239" s="1" t="s">
         <v>580</v>
@@ -9225,7 +9235,7 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>584</v>
@@ -9251,7 +9261,7 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>588</v>
@@ -9260,10 +9270,10 @@
         <v>589</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F241" s="1" t="s">
         <v>28</v>
@@ -9277,19 +9287,19 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>28</v>
@@ -9303,19 +9313,19 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>28</v>
@@ -9329,19 +9339,19 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>28</v>
@@ -9355,19 +9365,19 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>28</v>
@@ -9381,16 +9391,16 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>605</v>
+        <v>582</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>606</v>
@@ -9407,7 +9417,7 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>607</v>
@@ -9416,10 +9426,10 @@
         <v>608</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>530</v>
+        <v>609</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>28</v>
@@ -9433,19 +9443,19 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>28</v>
@@ -9459,19 +9469,19 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>28</v>
@@ -9485,7 +9495,7 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>616</v>
+        <v>530</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>617</v>
@@ -9494,7 +9504,7 @@
         <v>618</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>619</v>
@@ -9503,33 +9513,33 @@
         <v>28</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>549</v>
+        <v>621</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>550</v>
+        <v>622</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>354</v>
+        <v>623</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="H251" s="1" t="s">
         <v>146</v>
@@ -9537,19 +9547,19 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>620</v>
+        <v>553</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>621</v>
+        <v>554</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>530</v>
+        <v>357</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>622</v>
+        <v>358</v>
       </c>
       <c r="F252" s="1" t="s">
         <v>28</v>
@@ -9563,19 +9573,19 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>554</v>
+        <v>624</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>556</v>
+        <v>534</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>359</v>
+        <v>626</v>
       </c>
       <c r="F253" s="1" t="s">
         <v>28</v>
@@ -9589,19 +9599,19 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>623</v>
+        <v>558</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>624</v>
+        <v>559</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>625</v>
+        <v>363</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>28</v>
@@ -9615,19 +9625,19 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>28</v>
@@ -9641,19 +9651,19 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>538</v>
+        <v>357</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>28</v>
@@ -9667,19 +9677,19 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>353</v>
+        <v>542</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>28</v>
@@ -9693,19 +9703,19 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>538</v>
+        <v>357</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>28</v>
@@ -9719,19 +9729,19 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>353</v>
+        <v>542</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>28</v>
@@ -9745,19 +9755,19 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>530</v>
+        <v>357</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>28</v>
@@ -9771,19 +9781,19 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>28</v>
@@ -9797,19 +9807,19 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>530</v>
+        <v>357</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>28</v>
@@ -9823,19 +9833,19 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>28</v>
@@ -9849,19 +9859,19 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>530</v>
+        <v>357</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>28</v>
@@ -9875,19 +9885,19 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>28</v>
@@ -9901,19 +9911,19 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>530</v>
+        <v>357</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>28</v>
@@ -9927,19 +9937,19 @@
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>28</v>
@@ -9953,19 +9963,19 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>530</v>
+        <v>357</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>28</v>
@@ -9979,19 +9989,19 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>28</v>
@@ -10005,19 +10015,19 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>538</v>
+        <v>357</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>28</v>
@@ -10031,19 +10041,19 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>353</v>
+        <v>542</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>28</v>
@@ -10057,19 +10067,19 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>538</v>
+        <v>357</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>28</v>
@@ -10083,19 +10093,19 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>353</v>
+        <v>542</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>28</v>
@@ -10109,19 +10119,19 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>530</v>
+        <v>357</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>28</v>
@@ -10135,19 +10145,19 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>28</v>
@@ -10161,19 +10171,19 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>530</v>
+        <v>357</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>28</v>
@@ -10187,19 +10197,19 @@
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>28</v>
@@ -10213,19 +10223,19 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>530</v>
+        <v>357</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>28</v>
@@ -10239,19 +10249,19 @@
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>28</v>
@@ -10265,19 +10275,19 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>530</v>
+        <v>357</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>28</v>
@@ -10291,19 +10301,19 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>28</v>
@@ -10317,19 +10327,19 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>530</v>
+        <v>357</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>28</v>
@@ -10343,19 +10353,19 @@
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>28</v>
@@ -10369,19 +10379,19 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>530</v>
+        <v>357</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>28</v>
@@ -10395,19 +10405,19 @@
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>28</v>
@@ -10421,19 +10431,19 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>530</v>
+        <v>357</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>28</v>
@@ -10447,19 +10457,19 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>28</v>
@@ -10473,19 +10483,19 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>530</v>
+        <v>357</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>28</v>
@@ -10499,19 +10509,19 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>28</v>
@@ -10525,19 +10535,19 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>530</v>
+        <v>357</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>28</v>
@@ -10551,19 +10561,19 @@
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>28</v>
@@ -10577,19 +10587,19 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>530</v>
+        <v>357</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F292" s="1" t="s">
         <v>28</v>
@@ -10603,19 +10613,19 @@
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F293" s="1" t="s">
         <v>28</v>
@@ -10629,16 +10639,16 @@
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>745</v>
+        <v>357</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>746</v>
@@ -10655,7 +10665,7 @@
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>747</v>
@@ -10681,7 +10691,7 @@
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>751</v>
@@ -10690,10 +10700,10 @@
         <v>752</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>530</v>
+        <v>753</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F296" s="1" t="s">
         <v>28</v>
@@ -10707,19 +10717,19 @@
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>605</v>
+        <v>534</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>28</v>
@@ -10733,16 +10743,22 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>609</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
+      </c>
+      <c r="F298" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>14</v>
@@ -10753,23 +10769,19 @@
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="D299" s="1" t="s">
-        <v>745</v>
-      </c>
+        <v>762</v>
+      </c>
+      <c r="D299" s="1"/>
       <c r="E299" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="F299" s="1" t="s">
-        <v>28</v>
-      </c>
+        <v>763</v>
+      </c>
+      <c r="F299" s="1"/>
       <c r="G299" s="1" t="s">
         <v>14</v>
       </c>
@@ -10779,13 +10791,13 @@
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D300" s="1" t="s">
         <v>749</v>
@@ -10805,19 +10817,19 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>530</v>
+        <v>753</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>28</v>
@@ -10831,19 +10843,19 @@
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>605</v>
+        <v>534</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>28</v>
@@ -10857,16 +10869,22 @@
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>769</v>
+        <v>771</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>609</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>770</v>
+        <v>760</v>
+      </c>
+      <c r="F303" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G303" s="1" t="s">
         <v>14</v>
@@ -10877,23 +10895,19 @@
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="D304" s="1" t="s">
-        <v>745</v>
-      </c>
+        <v>773</v>
+      </c>
+      <c r="D304" s="1"/>
       <c r="E304" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="F304" s="1" t="s">
-        <v>28</v>
-      </c>
+        <v>774</v>
+      </c>
+      <c r="F304" s="1"/>
       <c r="G304" s="1" t="s">
         <v>14</v>
       </c>
@@ -10903,13 +10917,13 @@
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D305" s="1" t="s">
         <v>749</v>
@@ -10929,19 +10943,19 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>530</v>
+        <v>753</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>28</v>
@@ -10955,19 +10969,19 @@
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>605</v>
+        <v>534</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>28</v>
@@ -10981,16 +10995,22 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>780</v>
+        <v>782</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>609</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>781</v>
+        <v>760</v>
+      </c>
+      <c r="F308" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G308" s="1" t="s">
         <v>14</v>
@@ -11001,23 +11021,19 @@
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="D309" s="1" t="s">
-        <v>745</v>
-      </c>
+        <v>784</v>
+      </c>
+      <c r="D309" s="1"/>
       <c r="E309" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F309" s="1" t="s">
-        <v>28</v>
-      </c>
+        <v>785</v>
+      </c>
+      <c r="F309" s="1"/>
       <c r="G309" s="1" t="s">
         <v>14</v>
       </c>
@@ -11027,13 +11043,13 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="D310" s="1" t="s">
         <v>749</v>
@@ -11053,16 +11069,16 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>530</v>
+        <v>753</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>28</v>
@@ -11079,16 +11095,16 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>605</v>
+        <v>534</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>28</v>
@@ -11105,16 +11121,22 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>791</v>
+        <v>793</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>609</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>792</v>
+        <v>28</v>
+      </c>
+      <c r="F313" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G313" s="1" t="s">
         <v>14</v>
@@ -11125,23 +11147,19 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="D314" s="1" t="s">
-        <v>745</v>
-      </c>
+        <v>795</v>
+      </c>
+      <c r="D314" s="1"/>
       <c r="E314" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F314" s="1" t="s">
-        <v>28</v>
-      </c>
+        <v>796</v>
+      </c>
+      <c r="F314" s="1"/>
       <c r="G314" s="1" t="s">
         <v>14</v>
       </c>
@@ -11151,13 +11169,13 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D315" s="1" t="s">
         <v>749</v>
@@ -11177,16 +11195,16 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>530</v>
+        <v>753</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>28</v>
@@ -11203,16 +11221,16 @@
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>605</v>
+        <v>534</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>28</v>
@@ -11229,16 +11247,22 @@
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>802</v>
+        <v>804</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>609</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>803</v>
+        <v>28</v>
+      </c>
+      <c r="F318" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G318" s="1" t="s">
         <v>14</v>
@@ -11249,7 +11273,7 @@
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
-        <v>804</v>
+        <v>620</v>
       </c>
       <c r="B319" s="1" t="s">
         <v>805</v>
@@ -11257,25 +11281,21 @@
       <c r="C319" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="D319" s="1" t="s">
+      <c r="D319" s="1"/>
+      <c r="E319" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="E319" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="F319" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="F319" s="1"/>
       <c r="G319" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H319" s="1" t="s">
-        <v>14</v>
+        <v>146</v>
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B320" s="1" t="s">
         <v>809</v>
@@ -11284,10 +11304,10 @@
         <v>810</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>28</v>
@@ -11301,19 +11321,19 @@
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>530</v>
+        <v>811</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>28</v>
@@ -11327,19 +11347,19 @@
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>582</v>
+        <v>534</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>28</v>
@@ -11353,19 +11373,19 @@
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>432</v>
+        <v>586</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>28</v>
@@ -11374,30 +11394,30 @@
         <v>14</v>
       </c>
       <c r="H323" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="H324" s="1" t="s">
         <v>146</v>
@@ -11405,25 +11425,25 @@
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="H325" s="1" t="s">
         <v>146</v>
@@ -11431,19 +11451,19 @@
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>28</v>
@@ -11457,7 +11477,7 @@
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
-        <v>830</v>
+        <v>808</v>
       </c>
       <c r="B327" s="1" t="s">
         <v>831</v>
@@ -11466,11 +11486,11 @@
         <v>832</v>
       </c>
       <c r="D327" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="E327" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="E327" s="1" t="s">
-        <v>834</v>
-      </c>
       <c r="F327" s="1" t="s">
         <v>28</v>
       </c>
@@ -11478,12 +11498,12 @@
         <v>14</v>
       </c>
       <c r="H327" s="1" t="s">
-        <v>14</v>
+        <v>146</v>
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B328" s="1" t="s">
         <v>835</v>
@@ -11509,7 +11529,7 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B329" s="1" t="s">
         <v>839</v>
@@ -11521,7 +11541,7 @@
         <v>841</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>28</v>
@@ -11535,19 +11555,19 @@
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B330" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="E330" s="1" t="s">
         <v>842</v>
-      </c>
-      <c r="C330" s="1" t="s">
-        <v>843</v>
-      </c>
-      <c r="D330" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E330" s="1" t="s">
-        <v>838</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>28</v>
@@ -11561,19 +11581,19 @@
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>284</v>
+        <v>172</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>28</v>
@@ -11587,19 +11607,19 @@
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>183</v>
+        <v>288</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>28</v>
@@ -11613,19 +11633,19 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>284</v>
+        <v>172</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>28</v>
@@ -11639,19 +11659,19 @@
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>28</v>
@@ -11665,19 +11685,19 @@
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>11</v>
+        <v>288</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>28</v>
@@ -11691,19 +11711,19 @@
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>28</v>
@@ -11717,19 +11737,19 @@
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>284</v>
+        <v>59</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>28</v>
@@ -11743,19 +11763,19 @@
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="F338" s="1" t="s">
         <v>28</v>
@@ -11769,19 +11789,19 @@
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>183</v>
+        <v>288</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>862</v>
+        <v>842</v>
       </c>
       <c r="F339" s="1" t="s">
         <v>28</v>
@@ -11790,6 +11810,32 @@
         <v>14</v>
       </c>
       <c r="H339" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A340" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E340" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="F340" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G340" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H340" s="1" t="s">
         <v>14</v>
       </c>
     </row>

--- a/docs/Sundial_Customer__c_Field_Design.xlsx
+++ b/docs/Sundial_Customer__c_Field_Design.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2709" uniqueCount="867">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="870">
   <si>
     <t>Sundial Section</t>
   </si>
@@ -2615,6 +2615,15 @@
   </si>
   <si>
     <t>Appointment setter</t>
+  </si>
+  <si>
+    <t>Sales Rep Name</t>
+  </si>
+  <si>
+    <t>Sales_Rep_Name__c</t>
+  </si>
+  <si>
+    <t>The Sales Rep's name, set automatically. For list rows (the dealer list); the record page shows Sales Rep.</t>
   </si>
 </sst>
 </file>
@@ -3013,7 +3022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H340"/>
+  <dimension ref="A1:H341"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.5" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="30.875" style="1" customWidth="1"/>
@@ -11839,6 +11848,30 @@
         <v>14</v>
       </c>
     </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A341" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E341" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="F341" s="1"/>
+      <c r="G341" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H341" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Sundial_Customer__c_Field_Design.xlsx
+++ b/docs/Sundial_Customer__c_Field_Design.xlsx
@@ -10721,7 +10721,7 @@
         <v>14</v>
       </c>
       <c r="H296" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
@@ -10747,7 +10747,7 @@
         <v>14</v>
       </c>
       <c r="H297" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
@@ -10773,7 +10773,7 @@
         <v>14</v>
       </c>
       <c r="H298" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
@@ -10847,7 +10847,7 @@
         <v>14</v>
       </c>
       <c r="H301" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
@@ -10873,7 +10873,7 @@
         <v>14</v>
       </c>
       <c r="H302" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
@@ -10899,7 +10899,7 @@
         <v>14</v>
       </c>
       <c r="H303" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
@@ -10973,7 +10973,7 @@
         <v>14</v>
       </c>
       <c r="H306" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
@@ -10999,7 +10999,7 @@
         <v>14</v>
       </c>
       <c r="H307" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
@@ -11025,7 +11025,7 @@
         <v>14</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
@@ -11099,7 +11099,7 @@
         <v>14</v>
       </c>
       <c r="H311" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
@@ -11125,7 +11125,7 @@
         <v>14</v>
       </c>
       <c r="H312" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
@@ -11151,7 +11151,7 @@
         <v>14</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
@@ -11225,7 +11225,7 @@
         <v>14</v>
       </c>
       <c r="H316" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
@@ -11251,7 +11251,7 @@
         <v>14</v>
       </c>
       <c r="H317" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
@@ -11277,7 +11277,7 @@
         <v>14</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
